--- a/templates/students.xlsx
+++ b/templates/students.xlsx
@@ -3,7 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="3ème A" sheetId="1" r:id="rId1"/>
+    <sheet name="2nde B" sheetId="2" r:id="rId2"/>
+    <sheet name="Terminale C" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -397,39 +399,207 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:I2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Matricule</v>
+      </c>
+      <c r="B1" t="str">
         <v>Prénom*</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>Nom*</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Classe*</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>Date de naissance</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Nom parent</v>
+      </c>
+      <c r="G1" t="str">
         <v>Téléphone parent</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Nom parent 2</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Téléphone parent 2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Awa</v>
+        <v>STU-3A-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Kouassi</v>
+        <v>Exemple</v>
       </c>
       <c r="C2" t="str">
-        <v>3ème A</v>
+        <v>Eleve</v>
       </c>
       <c r="D2" t="str">
-        <v>2250700000001</v>
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>2011-10-21</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Parent 1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2250701020304</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Parent 2</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2250506070809</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Matricule</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Prénom*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Nom*</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Classe*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Date de naissance</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Nom parent</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Téléphone parent</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Nom parent 2</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Téléphone parent 2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>STU-2B-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Exemple</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Eleve</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>2010-04-09</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Parent 1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2250102030405</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Matricule</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Prénom*</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Nom*</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Classe*</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Date de naissance</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Nom parent</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Téléphone parent</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Nom parent 2</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Téléphone parent 2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>STU-TC-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Exemple</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Eleve</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>2008-01-15</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Parent 1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2250908070605</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/templates/students.xlsx
+++ b/templates/students.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,9 +424,12 @@
         <v>Téléphone parent</v>
       </c>
       <c r="H1" t="str">
+        <v>Email parent</v>
+      </c>
+      <c r="I1" t="str">
         <v>Nom parent 2</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Téléphone parent 2</v>
       </c>
     </row>
@@ -453,15 +456,18 @@
         <v>2250701020304</v>
       </c>
       <c r="H2" t="str">
+        <v>parent@exemple.com</v>
+      </c>
+      <c r="I2" t="str">
         <v>Parent 2</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>2250506070809</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
   </ignoredErrors>
 </worksheet>
 </file>
